--- a/Result/profitability/9930.xlsx
+++ b/Result/profitability/9930.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.91</v>
       </c>
       <c r="M2" t="n">
-        <v>1.28625</v>
+        <v>1.2775</v>
       </c>
       <c r="N2" t="n">
-        <v>16.75875</v>
+        <v>16.6675</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.99</v>
       </c>
       <c r="M3" t="n">
-        <v>1.26875</v>
+        <v>1.25375</v>
       </c>
       <c r="N3" t="n">
-        <v>18.94125</v>
+        <v>18.815</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.79</v>
       </c>
       <c r="M4" t="n">
-        <v>1.22</v>
+        <v>1.18625</v>
       </c>
       <c r="N4" t="n">
-        <v>20.735</v>
+        <v>20.42625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.88</v>
       </c>
       <c r="M5" t="n">
-        <v>1.16375</v>
+        <v>1.125</v>
       </c>
       <c r="N5" t="n">
-        <v>22.44125</v>
+        <v>22.20125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.85</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09875</v>
+        <v>1.0875</v>
       </c>
       <c r="N6" t="n">
-        <v>24.495</v>
+        <v>24.3275</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05625</v>
+        <v>1.04875</v>
       </c>
       <c r="N7" t="n">
-        <v>26.27875</v>
+        <v>26.1875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.68</v>
       </c>
       <c r="M8" t="n">
-        <v>1.00125</v>
+        <v>0.99625</v>
       </c>
       <c r="N8" t="n">
-        <v>27.995</v>
+        <v>27.8025</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.97</v>
       </c>
       <c r="M9" t="n">
-        <v>0.985</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>29.54125</v>
@@ -2026,7 +2026,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0.73625</v>
+        <v>0.7362500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>26.1675</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9930</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3382</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2927</v>
+      </c>
+      <c r="E75" t="n">
+        <v>456</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="G75" t="n">
+        <v>304</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>27</v>
+      </c>
+      <c r="J75" t="n">
+        <v>331</v>
+      </c>
+      <c r="K75" t="n">
+        <v>264</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.6875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.03636363636363638</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.539999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1025982678214523</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.3100000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2262773722627738</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1247563352826511</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
